--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486957_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486957_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5416</v>
+        <v>7.2547</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9651</v>
+        <v>7.3521</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4235</v>
+        <v>-0.0974</v>
       </c>
       <c r="G2" t="n">
         <v>1.8227</v>
@@ -610,13 +610,13 @@
         <v>4.1068</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3945</v>
+        <v>0.3186</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9649</v>
+        <v>0.4221</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4296</v>
+        <v>-0.1035</v>
       </c>
       <c r="V2" t="n">
         <v>3.0599</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5976</v>
+        <v>3.6338</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9923</v>
+        <v>2.0582</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6053</v>
+        <v>1.5757</v>
       </c>
       <c r="G3" t="n">
         <v>1.7917</v>
@@ -688,13 +688,13 @@
         <v>1.8481</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0461</v>
+        <v>0.0823</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3176</v>
+        <v>0.3834</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2715</v>
+        <v>-0.3011</v>
       </c>
       <c r="V3" t="n">
         <v>0.9384</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3484</v>
+        <v>3.5668</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6939</v>
+        <v>2.6238</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6545</v>
+        <v>0.9431</v>
       </c>
       <c r="G4" t="n">
         <v>-2.4782</v>
@@ -766,13 +766,13 @@
         <v>4.5175</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1957</v>
+        <v>1.4141</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6627999999999999</v>
+        <v>0.2671</v>
       </c>
       <c r="U4" t="n">
-        <v>1.8585</v>
+        <v>1.1471</v>
       </c>
       <c r="V4" t="n">
         <v>0.1134</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1798</v>
+        <v>0.7771</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0347</v>
+        <v>0.7209</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1451</v>
+        <v>0.0562</v>
       </c>
       <c r="G5" t="n">
         <v>0.1112</v>
@@ -844,13 +844,13 @@
         <v>0.4107</v>
       </c>
       <c r="S5" t="n">
-        <v>0.549</v>
+        <v>0.1463</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.6625</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4273</v>
+        <v>-0.5162</v>
       </c>
       <c r="V5" t="n">
         <v>0.1088</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X. TORRENT BAYÉ</t>
+          <t>X. OCHU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0804</v>
+        <v>-0.0751</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4318</v>
+        <v>-1.364</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5123</v>
+        <v>1.289</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.115</v>
+        <v>-2.8304</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8597</v>
+        <v>0.3771</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.2553</v>
+        <v>-3.2074</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4711</v>
+        <v>-2.5812</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4443</v>
+        <v>0.2346</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.0268</v>
+        <v>-2.8158</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6438</v>
+        <v>-0.2491</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4154</v>
+        <v>0.1425</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2284</v>
+        <v>-0.3916</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0267</v>
+        <v>2.0534</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R7" t="n">
         <v>3.0801</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5794</v>
+        <v>0.6974</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3248</v>
+        <v>0.825</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2546</v>
+        <v>-0.1277</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5893</v>
+        <v>0.0045</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7679</v>
+        <v>1.4189</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1786</v>
+        <v>-1.4144</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X. OCHU</t>
+          <t>X. TORRENT BAYÉ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5625</v>
+        <v>-0.4171</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4958</v>
+        <v>-1.1369</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9332</v>
+        <v>0.7198</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.8304</v>
+        <v>-3.115</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3771</v>
+        <v>-0.8597</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.2074</v>
+        <v>-2.2553</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.5812</v>
+        <v>-1.4711</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2346</v>
+        <v>-0.4443</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.8158</v>
+        <v>-1.0268</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2491</v>
+        <v>-1.6438</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1425</v>
+        <v>-0.4154</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3916</v>
+        <v>-1.2284</v>
       </c>
       <c r="P8" t="n">
-        <v>2.0534</v>
+        <v>1.0267</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R8" t="n">
         <v>3.0801</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2099</v>
+        <v>1.0818</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6933</v>
+        <v>0.6197</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4834</v>
+        <v>0.4621</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0045</v>
+        <v>0.5893</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4189</v>
+        <v>1.7679</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4144</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. LAROUSSE</t>
+          <t>P. SALA VALLMAJO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.992</v>
+        <v>-0.7559</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1227</v>
+        <v>-0.4994</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8693</v>
+        <v>-0.2565</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.7029</v>
+        <v>-1.3613</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2905</v>
+        <v>0.4963</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.4124</v>
+        <v>-1.8576</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4199</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2093</v>
+        <v>0.0779</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7893</v>
+        <v>-0.6974</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.283</v>
+        <v>-0.7418</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0813</v>
+        <v>0.4184</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.2017</v>
+        <v>-1.1602</v>
       </c>
       <c r="P9" t="n">
-        <v>1.2321</v>
+        <v>0.616</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2588</v>
+        <v>0.616</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4128</v>
+        <v>-0.0107</v>
       </c>
       <c r="T9" t="n">
-        <v>2.0221</v>
+        <v>0.1201</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3907</v>
+        <v>-0.1307</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9339</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2357</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. SALA VALLMAJO</t>
+          <t>F. ADEBAYO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0153</v>
+        <v>-1.8508</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-4.1865</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3454</v>
+        <v>2.3356</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3613</v>
+        <v>0.045</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4963</v>
+        <v>2.5892</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8576</v>
+        <v>-2.5442</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6195000000000001</v>
+        <v>1.9593</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0779</v>
+        <v>2.6965</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6974</v>
+        <v>-0.7372</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7418</v>
+        <v>-1.9144</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4184</v>
+        <v>-0.1074</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1602</v>
+        <v>-1.807</v>
       </c>
       <c r="P10" t="n">
-        <v>0.616</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-6.1603</v>
       </c>
       <c r="R10" t="n">
-        <v>0.616</v>
+        <v>4.5175</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2701</v>
+        <v>1.1613</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0504</v>
+        <v>0.7126</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2197</v>
+        <v>0.4487</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.4144</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.6982</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.7161999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. ADEBAYO</t>
+          <t>C. LAROUSSE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1029</v>
+        <v>-2.0702</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5274</v>
+        <v>-1.1416</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4246</v>
+        <v>-0.9286</v>
       </c>
       <c r="G11" t="n">
-        <v>0.045</v>
+        <v>-3.7029</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5892</v>
+        <v>-1.2905</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.5442</v>
+        <v>-2.4124</v>
       </c>
       <c r="J11" t="n">
-        <v>1.9593</v>
+        <v>-0.4199</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6965</v>
+        <v>-1.2093</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7372</v>
+        <v>0.7893</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9144</v>
+        <v>-3.283</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1074</v>
+        <v>-0.0813</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.807</v>
+        <v>-3.2017</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.1603</v>
+        <v>-1.0267</v>
       </c>
       <c r="R11" t="n">
-        <v>4.5175</v>
+        <v>2.2588</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9093</v>
+        <v>1.3346</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3717</v>
+        <v>1.0032</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5376</v>
+        <v>0.3314</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4144</v>
+        <v>-0.9339</v>
       </c>
       <c r="W11" t="n">
         <v>-0.6982</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.2357</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.439399999999999</v>
+        <v>10.4276</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4579</v>
+        <v>4.446099999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>5.9816</v>
+        <v>5.981699999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-9.279300000000001</v>
@@ -1363,13 +1363,13 @@
         <v>-14.3915</v>
       </c>
       <c r="J12" t="n">
-        <v>5.093800000000002</v>
+        <v>5.093800000000001</v>
       </c>
       <c r="K12" t="n">
         <v>5.2278</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1340000000000007</v>
+        <v>-0.1340000000000006</v>
       </c>
       <c r="M12" t="n">
         <v>-14.373</v>
@@ -1390,13 +1390,13 @@
         <v>24.6409</v>
       </c>
       <c r="S12" t="n">
-        <v>4.958699999999999</v>
+        <v>5.946800000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>4.027699999999999</v>
+        <v>5.015700000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9309999999999999</v>
+        <v>0.9312</v>
       </c>
       <c r="V12" t="n">
         <v>2.466</v>
@@ -1405,7 +1405,7 @@
         <v>7.6835</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.2175</v>
+        <v>-5.217499999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.5501</v>
+        <v>6.0408</v>
       </c>
       <c r="E13" t="n">
-        <v>6.764</v>
+        <v>7.3916</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2139</v>
+        <v>-1.3508</v>
       </c>
       <c r="G13" t="n">
         <v>9.161799999999999</v>
@@ -1468,13 +1468,13 @@
         <v>1.4374</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6834</v>
+        <v>-0.1927</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9222</v>
+        <v>-0.2946</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7612</v>
+        <v>0.1019</v>
       </c>
       <c r="V13" t="n">
         <v>1.1786</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. RIVAS PALMER</t>
+          <t>V. PEREZ TOMAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1353</v>
+        <v>3.5417</v>
       </c>
       <c r="E14" t="n">
-        <v>1.639</v>
+        <v>2.4443</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4963</v>
+        <v>1.0974</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1753</v>
+        <v>4.7873</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.3502</v>
+        <v>-0.1172</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5254</v>
+        <v>4.9045</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2208</v>
+        <v>4.6257</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.5806</v>
+        <v>0.3504</v>
       </c>
       <c r="L14" t="n">
-        <v>2.8013</v>
+        <v>4.2753</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0455</v>
+        <v>0.1615</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7696</v>
+        <v>-0.4676</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2759</v>
+        <v>0.6291</v>
       </c>
       <c r="P14" t="n">
-        <v>0.8214</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.8214</v>
+        <v>-1.8481</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6427</v>
+        <v>1.4374</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8332000000000001</v>
+        <v>-0.5511</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3485</v>
+        <v>-0.3333</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4847</v>
+        <v>-0.2178</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3055</v>
+        <v>-0.2838</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.1088</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.4144</v>
+        <v>-0.2838</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. PEREZ TOMAS</t>
+          <t>D. RIVAS PALMER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.731</v>
+        <v>2.6471</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9213</v>
+        <v>1.3252</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8097</v>
+        <v>1.3219</v>
       </c>
       <c r="G15" t="n">
-        <v>4.7873</v>
+        <v>1.1753</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1172</v>
+        <v>-1.3502</v>
       </c>
       <c r="I15" t="n">
-        <v>4.9045</v>
+        <v>2.5254</v>
       </c>
       <c r="J15" t="n">
-        <v>4.6257</v>
+        <v>2.2208</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3504</v>
+        <v>-0.5806</v>
       </c>
       <c r="L15" t="n">
-        <v>4.2753</v>
+        <v>2.8013</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1615</v>
+        <v>-1.0455</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4676</v>
+        <v>-0.7696</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6291</v>
+        <v>-0.2759</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.8481</v>
+        <v>-0.8214</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3618</v>
+        <v>0.3449</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8563</v>
+        <v>0.0347</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5054</v>
+        <v>0.3102</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2838</v>
+        <v>0.3055</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.1088</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2838</v>
+        <v>0.4144</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7792</v>
+        <v>1.2778</v>
       </c>
       <c r="E16" t="n">
         <v>-0.3015</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0808</v>
+        <v>1.5794</v>
       </c>
       <c r="G16" t="n">
         <v>0.0433</v>
@@ -1702,13 +1702,13 @@
         <v>1.6427</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1286</v>
+        <v>0.37</v>
       </c>
       <c r="T16" t="n">
         <v>0.1122</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2408</v>
+        <v>0.2578</v>
       </c>
       <c r="V16" t="n">
         <v>0.6591</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1276</v>
+        <v>0.2751</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6504</v>
+        <v>0.5458</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7781</v>
+        <v>-0.2707</v>
       </c>
       <c r="G17" t="n">
         <v>0.216</v>
@@ -1780,13 +1780,13 @@
         <v>1.2321</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.549</v>
+        <v>-0.1463</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1122</v>
+        <v>0.0076</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6612</v>
+        <v>-0.1539</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0194</v>
+        <v>-2.334</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.9941</v>
+        <v>-3.9355</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9747</v>
+        <v>1.6015</v>
       </c>
       <c r="G18" t="n">
         <v>-1.1415</v>
@@ -1858,13 +1858,13 @@
         <v>2.0534</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1961</v>
+        <v>0.8814</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5651</v>
+        <v>0.6237</v>
       </c>
       <c r="U18" t="n">
-        <v>0.631</v>
+        <v>0.2578</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0472</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.0177</v>
+        <v>-2.7195</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0148</v>
+        <v>-2.224</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0029</v>
+        <v>-0.4955</v>
       </c>
       <c r="G19" t="n">
         <v>0.4346</v>
@@ -1936,13 +1936,13 @@
         <v>1.2321</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4909</v>
+        <v>-0.1927</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2362</v>
+        <v>0.027</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7271</v>
+        <v>-0.2198</v>
       </c>
       <c r="V19" t="n">
         <v>-0.7027</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.2554</v>
+        <v>-3.211</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.9286</v>
+        <v>-3.5102</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3267</v>
+        <v>0.2992</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4146</v>
@@ -2014,13 +2014,13 @@
         <v>1.2321</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5857</v>
+        <v>-0.5414</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5192</v>
+        <v>-0.1008</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0665</v>
+        <v>-0.4406</v>
       </c>
       <c r="V20" t="n">
         <v>1.0037</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.7079</v>
+        <v>-5.2406</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.0944</v>
+        <v>-3.8852</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6135</v>
+        <v>-1.3555</v>
       </c>
       <c r="G21" t="n">
         <v>-3.9845</v>
@@ -2092,13 +2092,13 @@
         <v>0.8214</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3661</v>
+        <v>-0.8988</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7905</v>
+        <v>-0.5813</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5756</v>
+        <v>-0.3176</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1786</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.5072</v>
+        <v>-6.23</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.623</v>
+        <v>-3.8322</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8842</v>
+        <v>-2.3978</v>
       </c>
       <c r="G22" t="n">
         <v>0.0015</v>
@@ -2170,13 +2170,13 @@
         <v>0.616</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8225</v>
+        <v>-0.5453</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2171</v>
+        <v>-0.4263</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6054</v>
+        <v>-0.1189</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4008</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.439600000000002</v>
+        <v>-5.952599999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.981700000000001</v>
+        <v>-5.9817</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.4578</v>
+        <v>0.02909999999999968</v>
       </c>
       <c r="G23" t="n">
         <v>9.279199999999999</v>
@@ -2224,7 +2224,7 @@
         <v>14.373</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1153999999999999</v>
+        <v>0.1154000000000002</v>
       </c>
       <c r="L23" t="n">
         <v>14.2575</v>
@@ -2248,13 +2248,13 @@
         <v>13.3473</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.958699999999999</v>
+        <v>-1.472</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9311000000000001</v>
+        <v>-0.9310999999999998</v>
       </c>
       <c r="U23" t="n">
-        <v>-4.0275</v>
+        <v>-0.5409</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4662</v>
